--- a/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,320 +656,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1705600</v>
+        <v>1829900</v>
       </c>
       <c r="E8" s="3">
+        <v>1864600</v>
+      </c>
+      <c r="F8" s="3">
         <v>1799400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1758000</v>
       </c>
-      <c r="G8" s="3">
-        <v>1657300</v>
-      </c>
       <c r="H8" s="3">
-        <v>1664100</v>
+        <v>1566500</v>
       </c>
       <c r="I8" s="3">
+        <v>1801500</v>
+      </c>
+      <c r="J8" s="3">
         <v>1663000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1889100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1489700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2219900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1264600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2101400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1748600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2091700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3462200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2792200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2487200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2264400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2026000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1862200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1787500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1722100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1728200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1749800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1857400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2028100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2216400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2287800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2353100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2369400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2154000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2006200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1989700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1910800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1912500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1925300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1853100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1833700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1898800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E9" s="3">
         <v>5700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9400</v>
-      </c>
-      <c r="N9" s="3">
-        <v>6800</v>
       </c>
       <c r="O9" s="3">
         <v>6800</v>
       </c>
       <c r="P9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Q9" s="3">
         <v>7100</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1045,53 +1051,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1700000</v>
+        <v>1824300</v>
       </c>
       <c r="E10" s="3">
+        <v>1858900</v>
+      </c>
+      <c r="F10" s="3">
         <v>1792700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1751200</v>
       </c>
-      <c r="G10" s="3">
-        <v>1650900</v>
-      </c>
       <c r="H10" s="3">
-        <v>1658200</v>
+        <v>1560100</v>
       </c>
       <c r="I10" s="3">
+        <v>1795600</v>
+      </c>
+      <c r="J10" s="3">
         <v>1656000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1881500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1482800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2212800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1255200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2094600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1741800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2084600</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1167,8 +1176,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1211,8 +1223,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1333,8 +1346,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1455,53 +1471,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F14" s="3">
         <v>78600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-385700</v>
       </c>
-      <c r="G14" s="3">
-        <v>23100</v>
-      </c>
       <c r="H14" s="3">
-        <v>200</v>
+        <v>-600</v>
       </c>
       <c r="I14" s="3">
+        <v>800</v>
+      </c>
+      <c r="J14" s="3">
         <v>6200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>8400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1700</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>42300</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1577,130 +1596,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>206700</v>
+      </c>
+      <c r="E15" s="3">
         <v>208900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>291800</v>
       </c>
-      <c r="F15" s="3">
-        <v>111700</v>
-      </c>
       <c r="G15" s="3">
-        <v>112700</v>
+        <v>109600</v>
       </c>
       <c r="H15" s="3">
+        <v>228500</v>
+      </c>
+      <c r="I15" s="3">
         <v>210100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>282800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>108500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>205400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>144200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>130600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>130000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>130100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-101500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-92100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-100700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-101400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-98200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-97600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-97400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-100600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-99400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-99600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-96100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-109500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-115200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-112100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-104100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-88900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-50500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-47800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-44700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-40700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-39500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-40300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-40800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-44500</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-54800</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-53700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1740,252 +1765,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1164700</v>
+        <v>1000000</v>
       </c>
       <c r="E17" s="3">
+        <v>1323700</v>
+      </c>
+      <c r="F17" s="3">
         <v>1298800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1041000</v>
       </c>
-      <c r="G17" s="3">
-        <v>826800</v>
-      </c>
       <c r="H17" s="3">
-        <v>1073900</v>
+        <v>736000</v>
       </c>
       <c r="I17" s="3">
+        <v>1211300</v>
+      </c>
+      <c r="J17" s="3">
         <v>1203500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>979300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>578900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1363800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1160500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1189600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1049500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1131700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1897900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1245200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1121400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>861300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>772200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>616800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>573600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>625700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>727900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>721100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>966200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>926000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1019500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1190700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1111900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1098300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1157200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>918800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>752200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>877900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1026000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>926800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>906500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>830000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>903100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>963600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>830000</v>
+      </c>
+      <c r="E18" s="3">
         <v>540900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>500500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>717000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>830500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>590100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>459500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>909700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>910800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>856000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>104100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>911700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>699100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>960100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1564300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1547000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1365800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1403000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1253800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1245400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1213900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1096400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1000300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1028700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>891200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1102100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1196900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1097100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1241200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1271100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>996800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1087400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1237400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1032900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>886500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>998500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>946600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1003700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>995700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>934400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2028,252 +2060,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-20400</v>
+        <v>-21300</v>
       </c>
       <c r="E20" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="F20" s="3">
         <v>68600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>14200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-69300</v>
-      </c>
       <c r="H20" s="3">
-        <v>2800</v>
+        <v>-45600</v>
       </c>
       <c r="I20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J20" s="3">
         <v>26000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-14500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>32600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-56500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1017300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-606600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-375600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-505900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-806400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-394200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-406900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-399500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-784600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-508200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-674600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-492400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-920900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-527400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-447200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-519600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-847700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-418500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-401200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-355800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-756300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-671500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-417500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-274500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-821100</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>770300</v>
+        <v>1057900</v>
       </c>
       <c r="E21" s="3">
+        <v>763200</v>
+      </c>
+      <c r="F21" s="3">
         <v>723800</v>
       </c>
-      <c r="F21" s="3">
-        <v>814500</v>
-      </c>
       <c r="G21" s="3">
-        <v>1012500</v>
+        <v>812400</v>
       </c>
       <c r="H21" s="3">
-        <v>797400</v>
+        <v>1104600</v>
       </c>
       <c r="I21" s="3">
+        <v>798100</v>
+      </c>
+      <c r="J21" s="3">
         <v>716400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1022700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>919700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1068900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>236700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1056800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>796500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1146700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>732200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1110000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1165700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1065700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>603300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1000500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>991500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>799800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>316900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>622000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>315300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>721900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>396300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>686600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>902900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>845100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>210800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>727400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>892200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>727700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>180100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>377800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>580800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>784400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>229400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>457200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2316,8 +2355,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2394,252 +2433,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>851200</v>
+      </c>
+      <c r="E23" s="3">
         <v>557200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>353300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1088400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>876700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>587100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>427300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>914200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>904900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>851200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>94200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>926200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>666800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>974300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>546900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>940400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>990200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>897100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>447400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>851200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>807000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>696900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>215700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>520500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>216600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>609600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>276000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>569700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>794000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>751500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>149100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>668900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>836200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>677100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>130200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>327000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>529200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>729200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>174600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>403400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>188400</v>
+      </c>
+      <c r="E24" s="3">
         <v>137100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>116600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>169100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>182300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>142600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>120000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>216000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>207100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>227000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>21000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>244100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>160200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>248300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>148500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>259000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>240200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>225300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>113100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>232900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>193200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>164900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>53200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>118800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>50000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>157800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>79200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>115700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>215500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>192300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>39300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>179200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>229900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>177700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>9000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>77600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>118800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>163600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>30300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2760,252 +2808,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>662800</v>
+      </c>
+      <c r="E26" s="3">
         <v>420100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>236700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>919400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>694400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>444500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>307400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>698200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>697800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>624200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>73200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>682000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>506600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>726000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>398500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>681400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>750000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>671800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>334300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>618300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>613800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>532000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>162400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>401700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>166500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>451800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>196800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>454000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>578500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>559200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>109900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>489700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>606300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>499400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>121100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>249400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>410300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>565600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>144300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>623500</v>
+      </c>
+      <c r="E27" s="3">
         <v>371400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>201700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>859000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>664400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>391900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>261600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>655100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>647100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>586900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>25300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>643700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>449800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>677400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>338800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>640600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>684400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>631400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>279500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>570700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>552600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>482000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>112600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>358800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>100500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>412900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>174900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>410100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>537700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>517500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>76800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>453900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>569900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>463600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>84900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>212100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>369000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>517600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>88500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3126,8 +3183,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3248,8 +3308,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3370,8 +3433,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3492,252 +3558,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>20400</v>
+        <v>21300</v>
       </c>
       <c r="E32" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-68600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-14200</v>
       </c>
-      <c r="G32" s="3">
-        <v>69300</v>
-      </c>
       <c r="H32" s="3">
-        <v>-2800</v>
+        <v>45600</v>
       </c>
       <c r="I32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J32" s="3">
         <v>-26000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>14500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-32600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>56500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1017300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>606600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>375600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>505900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>806400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>394200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>406900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>399500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>784600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>508200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>674600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>492400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>920900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>527400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>447200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>519600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>847700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>418500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>401200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>355800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>756300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>671500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>417500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>274500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>821100</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>648700</v>
+      </c>
+      <c r="E33" s="3">
         <v>397000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>227500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>885500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>691100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>418800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>288500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>688600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>676000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>613100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>52500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>668000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>474700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>700700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>338800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>640600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>684400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>631400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>279500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>570700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>552600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>482000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>112600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>358800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>100500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>412900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>174900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>410100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>537700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>517500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>76800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>453900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>569900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>463600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>84900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>212100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>369000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>517600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>88500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3858,257 +3933,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>648700</v>
+      </c>
+      <c r="E35" s="3">
         <v>397000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>227500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>885500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>691100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>418800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>288500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>688600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>676000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>613100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>52500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>668000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>474700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>700700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>338800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>640600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>684400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>631400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>279500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>570700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>552600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>482000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>112600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>358800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>100500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>412900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>174900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>410100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>537700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>517500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>76800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>453900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>569900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>463600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>84900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>212100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>369000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>517600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>88500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4151,8 +4235,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4195,297 +4280,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11290900</v>
+      </c>
+      <c r="E41" s="3">
         <v>12856600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10408300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10043000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9721700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9800400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9892700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13834100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8534800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13129900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12476200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7157900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9809900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10234100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>25596900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6507700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7377100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9785500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5555400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7893500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7303900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7996900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6985700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6452400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6934700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7810800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5327800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7069900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5777500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4361000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5329900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4608100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4589200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4387400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5323900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5337600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>5780800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>6495200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>6385500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>7024600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>30622800</v>
+      </c>
+      <c r="E42" s="3">
         <v>29672100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>30478600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>33934900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>29338000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26987000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22818100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>29370000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>19283100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18486700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18215800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>17492100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>25108400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17703400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>41084100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>48087900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>44907700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>44616700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>44083500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>38326100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>33800600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>32013900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>39170300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>33273800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>36396600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>38606200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>37680800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>39232200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>36892000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>30905300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>29776700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>20883600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>22286700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>21840100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>20932300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>12488600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>14955900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>13350900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>14204100</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>16154100</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19500200</v>
+      </c>
+      <c r="E43" s="3">
         <v>14652700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7082500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13780300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15335100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12353800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6099900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13077600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9540700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10078300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8598900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9843900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11594400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10468300</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4561,8 +4653,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4605,8 +4700,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4683,53 +4778,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2691200</v>
+      </c>
+      <c r="E45" s="3">
         <v>2425900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5813900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2491200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2304800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1984500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3417100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2191600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2546100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2248400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3229200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2254000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2036900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1992400</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4805,53 +4903,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>77841200</v>
+      </c>
+      <c r="E46" s="3">
         <v>69807000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>70334000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>71300600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>69444800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>58995800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>51046100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>70438600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>50125600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>54875900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>53874000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>49079800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>55527700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>55109700</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4927,374 +5028,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>62494400</v>
+      </c>
+      <c r="E47" s="3">
         <v>64066400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>51061400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>64194100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>44237900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>43339500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>29491700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43909700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45684200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>45083200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>33573300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>46697400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>47231400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>47653400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>979200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>976800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1035000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1011300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1001400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>896000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>881500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>775800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>735000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>829200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>714700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>674300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>685400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>322100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>311500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>316200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>303600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>276700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>346900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>348200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>367000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>490900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>326300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>351100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>395100</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>377600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6300900</v>
+      </c>
+      <c r="E48" s="3">
         <v>6456400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5254900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5401200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5310400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4933500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4937200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5522800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5103100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4908300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4983700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4486300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4434900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4401200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2648000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2590300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2689200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2729900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2673200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2701000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2682600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2700600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2719200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2764300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2790300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2961700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3098200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3089800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3058200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3080600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2368100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2284800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2378800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2384000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2507000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2509800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2480800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2470200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2534900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2525400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>680500</v>
+      </c>
+      <c r="E49" s="3">
         <v>697900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>503500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>770100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>788000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>745500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>552200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>621800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>557800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>562600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>582000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>568100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>586300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>573300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>636800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>639200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>596500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>608700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>589000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>586400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>581700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>582600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>586100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>615800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>631700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>668000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>717500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>590200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>565800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>588900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>493300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>502400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>549000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>452700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>456400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>461900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>446100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>415100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>435400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>376700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5415,8 +5528,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5537,130 +5653,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5717900</v>
+      </c>
+      <c r="E52" s="3">
         <v>5004100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22900500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5286500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1343400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1099500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15436000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1117800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1097200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1375500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16836600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1488400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1186200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1174600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>331800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>284500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>166400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>58400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>59100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>41100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>56000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>73700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>82700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>74500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>37800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>38200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>44800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>82300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>69500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>68200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>120400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>36800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>91100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>177600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>289300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>234800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>221100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>262700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>274800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5781,130 +5903,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>410161000</v>
+      </c>
+      <c r="E54" s="3">
         <v>402432700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>416660200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>417822000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>394651000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>361721400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>355900000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>413964600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>369217100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>375587700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>384037900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>360962600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>366653200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>366661700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>360355800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>366510300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>368558700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>358592300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>335387900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>328638700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>315953000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>307917200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>295320000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>293246000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>292659600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>306353500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>307683600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>314996600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>316273500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>314085600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>285975600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>267139300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>274311500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>273668600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>278340000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>279730100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>278137400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>273600800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>279614500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>281548700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5947,8 +6075,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5991,175 +6120,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>262018400</v>
+      </c>
+      <c r="E57" s="3">
         <v>258292200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>266776300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>276347000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>287825900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>262183700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>253583100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>303683400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>269353200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>273669100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>283746600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>257925300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>263215600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>259046400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8592200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12736100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12538100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11104000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10844700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7957500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9468900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7995800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3698600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7530800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8467000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9538600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7264700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13339700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>15138200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>14778600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10988500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12068900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11638400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>12317300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>5801500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>13814400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>14756900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>13329400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>15356600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13049000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11982900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11198400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9091100</v>
       </c>
-      <c r="G58" s="3">
-        <v>8966800</v>
-      </c>
       <c r="H58" s="3">
+        <v>9126400</v>
+      </c>
+      <c r="I58" s="3">
         <v>10611200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12014400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10388900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10701400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11337600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9863100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11103300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10559700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10550500</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6235,175 +6368,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>751400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1190800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1226800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1113600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1084300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>825800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>747300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>917100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>585700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>748600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>795100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>581800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>593500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1203800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3047200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2229700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1968300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2093100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1991300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1538600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1446500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1600800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1790900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1521700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1545300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1892000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2294100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2199800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2064700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2149400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1989900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1798500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1649500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1642100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2057400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1681400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1880000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2004400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1813400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>278639400</v>
+      </c>
+      <c r="E60" s="3">
         <v>274242200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>282288500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>289912100</v>
       </c>
-      <c r="G60" s="3">
-        <v>301362800</v>
-      </c>
       <c r="H60" s="3">
+        <v>301522400</v>
+      </c>
+      <c r="I60" s="3">
         <v>276760100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>269522700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>318811800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>283969800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>288965400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>297751000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>272946300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>277365200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>273486900</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6479,252 +6618,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>62436200</v>
+      </c>
+      <c r="E61" s="3">
         <v>56538600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>61015700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>57103900</v>
       </c>
-      <c r="G61" s="3">
-        <v>58864300</v>
-      </c>
       <c r="H61" s="3">
+        <v>58704700</v>
+      </c>
+      <c r="I61" s="3">
         <v>51786600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>52292900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>57884900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51737100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>52671400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>54929200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>53360000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>54858600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>55629400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>52670100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>58817800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>58413400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>54512100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>51506600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>49335300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>46999300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>43329900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>42586400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>38230600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>39214800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>43080800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>42129500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>44185000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>43142100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>40307800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>36868700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>34955700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>35115500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>34009900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>36941800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>37408900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>35000000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>33280700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>34538700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>33926000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>41067300</v>
+      </c>
+      <c r="E62" s="3">
         <v>43878000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>46041700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>42772800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6912600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7918500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8428000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8065900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6973100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7766400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4724200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8885900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8657200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11788800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>459600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>438000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>469900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>523500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>608300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>663300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>620300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>542300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>528500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>720700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>691400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>680000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>570200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>714600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>648100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>618700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>520300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>418500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>420800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>527700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>419200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>395900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>382900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>400700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>463600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6845,8 +6993,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6967,8 +7118,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7089,130 +7243,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>383763100</v>
+      </c>
+      <c r="E66" s="3">
         <v>376216600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>390433100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>391375900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>368261100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>337599900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>331601300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>386400900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>343710800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>350345300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>358283300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>336284100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>341832200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>341656500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>338784400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>345885900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>348018900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>338354200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>316006400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>309651700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>297533600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>290517700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>278260300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>275726000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>275487700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>288675900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>289399800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>297278600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>299163500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>296968200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>267714100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>249559900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>256847800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>256582900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>260418000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>261733600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>260311800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>255640700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>261266900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>263136400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7255,8 +7415,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7377,8 +7538,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7499,8 +7663,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7621,8 +7788,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7743,130 +7913,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18987100</v>
+      </c>
+      <c r="E72" s="3">
         <v>18918300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19944300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20390800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20492400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18322200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18243700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20282200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18807000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18719000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19268400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18710700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18565400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18299100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17812600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17007700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17130600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16662400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>16044400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15764300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15298800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14524300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14258500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14719300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14362200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15002800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15745800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15573800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15698600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15678000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14384700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13795900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13837700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>13273900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>13745600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>13660700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>13507800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>13138800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>13150400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>13062800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7987,8 +8163,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8109,8 +8288,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8231,130 +8413,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25109400</v>
+      </c>
+      <c r="E76" s="3">
         <v>24969000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24951000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25167700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25252000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22902500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23081300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25698700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24286300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23977100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24420000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23463000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22963400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22747400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21571400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20624400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20539800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20238100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19381500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18987000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18419400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17399500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17059700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17519900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17171900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17677500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18283800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17718000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17110000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17117400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18261500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17579400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>17463800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>17085700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17922000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>17996500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>17825600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>17960100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>18347500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>18412300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8475,257 +8663,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>648700</v>
+      </c>
+      <c r="E81" s="3">
         <v>397000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>227500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>885500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>691100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>418800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>288500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>688600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>676000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>613100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>52500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>668000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>474700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>700700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>338800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>640600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>684400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>631400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>279500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>570700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>552600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>482000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>112600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>358800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>100500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>412900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>174900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>410100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>537700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>517500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>76800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>453900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>569900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>463600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>84900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>212100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>369000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>517600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>88500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8768,130 +8965,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>222500</v>
+      </c>
+      <c r="E83" s="3">
         <v>204600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>106200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>218200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>204400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>173700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>150800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>153800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>154400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>162700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>133200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>147300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>148000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>185200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>169700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>175600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>168600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>155900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>149200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>184500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>102900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>101300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>101500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>98700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>112300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>120400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>116900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>108900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>93600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>61600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>58600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>56000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>50600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>49900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>50800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>51600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>55200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>54800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9012,8 +9213,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9134,8 +9338,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9256,8 +9463,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9378,8 +9588,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9500,130 +9713,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5842000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2570700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-342000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6204800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4742200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1359600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15238500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-21513100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5708900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3028800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13351300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3754000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11714900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10840700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12011900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3350300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2130300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7700600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4027400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2586700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4607300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>831700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1545900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-766500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2718500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-824700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-153300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-428600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3501700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1296100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5231600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>908000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>643600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>877700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-506300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-340700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1561500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>108800</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>3807600</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9666,130 +9885,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-142900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-66200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-32300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-62500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-61300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-113722000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-77226000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-104059000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-52618000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-74615000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-81614000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-43600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-25600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-190900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-55400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-31700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-57300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-37900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9910,8 +10133,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10032,130 +10258,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1208200</v>
+      </c>
+      <c r="E94" s="3">
         <v>647000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7655100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1956500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2605800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>265900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3917800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3642700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1092400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1841100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-625400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1107500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-261600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>300800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2910400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2354900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2353800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2278800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4489600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3902300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1124900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-723400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-365200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-124500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-446100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-179800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-962200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-913600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5520900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-97900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5105000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2452600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-587600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>1277600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-195600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>183200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>392500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2371700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>694800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10198,59 +10430,60 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>486900</v>
+      </c>
+      <c r="E96" s="3">
         <v>25600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>127000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>130500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>495800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>26800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>117000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>134900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>473000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>26200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>151100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>102000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>566300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>23300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-79700</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -10258,11 +10491,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-81300</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -10306,22 +10539,25 @@
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-22800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10442,8 +10678,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10564,8 +10803,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10686,370 +10928,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9083300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6514600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>14210100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5092600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6108300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-68000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-16521000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>24357600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1880400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4107500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>17753300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>447300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5022900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13746200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5147300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1697300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3000400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1932700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2031800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1404600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2911000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>453200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>261800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>553800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2356000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3526800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-950700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3000500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>3588600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-289800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>491400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1689200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>354700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1323700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-309500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>2140800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-384900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1500100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1503800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1778900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-720100</v>
+      </c>
+      <c r="E101" s="3">
         <v>25300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-385300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>231000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>262700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-179300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>27300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-105100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>125800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1568200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>609200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>667200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>217100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1479100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>638600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>657000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>203100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>68900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>409500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>18100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>295500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-571700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-142900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-159900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>200400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>369400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-340600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>51200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>90500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>6400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-76600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>218900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>50500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-377500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>14000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>8400</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-108300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>138000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-105900</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2381200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2581300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6419800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-552400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3251800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1136400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4200200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6101900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4689900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1025100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3597300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3121100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7058600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2478800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2475100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3369400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3880900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>7557600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1638600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>498500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-553300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>857000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>870800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-480000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-243500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2722600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1317700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1620600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1593300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>624400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>68000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>153400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-983000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>84300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-496900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-534100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>345600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-621200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>2617600</v>
       </c>
     </row>
